--- a/04_DESIGN_TABLES/DesignTable_2501L.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2501L.xlsx
@@ -546,7 +546,7 @@
         <v>0.89</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0.44</v>
@@ -580,12 +580,12 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s119 only (double-pass 21 rows); M leg matches verified 2501 family; N3 long leg single-source; JIC end VERIFIED (MS33656J)</t>
+          <t>Air-Way s119 only (double-pass 21 rows); M leg matches verified 2501 family; N3 long leg single-source; JIC end VERIFIED (MS33656J); N3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P703 = 1.170 (table had 1.19) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>M matches verified 2501 M family</t>
+          <t>M matches verified 2501 M family | A19 (user 2026-10-18, group 2 settled): N3@DRIVE 1.19 -&gt; OMi 1.170 (Items!P703, M077)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -1057,7 +1057,11 @@
           <t>Air-Way s119 only (double-pass 21 rows); M leg matches verified 2501 family; N3 long leg single-source; JIC end VERIFIED (MS33656J)</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M@DRIVE=1.14~1.140; N3@DRIVE=1.82~1.820; Y@REF=0.75~0.750; D@BORE=0.3~0.297; D1@BORE=0.41~0.406</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>BUILD</t>

--- a/04_DESIGN_TABLES/DesignTable_2501L.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2501L.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,7 +546,7 @@
         <v>0.89</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0.44</v>
@@ -580,12 +580,12 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s119 only (double-pass 21 rows); M leg matches verified 2501 family; N3 long leg single-source; JIC end VERIFIED (MS33656J); N3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P703 = 1.170 (table had 1.19) [user 2026-10-18 A19]</t>
+          <t>Air-Way s119 only (double-pass 21 rows); M leg matches verified 2501 family; N3 long leg single-source; JIC end VERIFIED (MS33656J); N3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P703 = 1.170 (table had 1.19) [user 2026-10-18 A19]; N3@DRIVE: Air-Way 1.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.17) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>M matches verified 2501 M family | A19 (user 2026-10-18, group 2 settled): N3@DRIVE 1.19 -&gt; OMi 1.170 (Items!P703, M077)</t>
+          <t>M matches verified 2501 M family | A19 (user 2026-10-18, group 2 settled): N3@DRIVE 1.19 -&gt; OMi 1.170 (Items!P703, M077) | 2026-10-20 Air-Way first: N3@DRIVE OMi/Brennan 1.17 -&gt; Air-Way 1.19</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
